--- a/artfynd/A 46162-2023 artfynd.xlsx
+++ b/artfynd/A 46162-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46162-2023 artfynd.xlsx
+++ b/artfynd/A 46162-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108507984</v>
+        <v>111595763</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fallet, Upl</t>
+          <t>Granlunda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625934.3612157413</v>
+        <v>625973</v>
       </c>
       <c r="R2" t="n">
-        <v>6657695.493227109</v>
+        <v>6657703</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108507998</v>
+        <v>108508010</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626136.4026928359</v>
+        <v>626056</v>
       </c>
       <c r="R3" t="n">
-        <v>6657660.904246838</v>
+        <v>6657833</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,19 +845,14 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rotbenet på rötad granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108508002</v>
+        <v>108508013</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626084.1613645289</v>
+        <v>626001</v>
       </c>
       <c r="R4" t="n">
-        <v>6657709.120220892</v>
+        <v>6657868</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -972,19 +947,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108507980</v>
+        <v>108507985</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625939.2912217755</v>
+        <v>625930</v>
       </c>
       <c r="R5" t="n">
-        <v>6657785.6693347</v>
+        <v>6657649</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1084,24 +1044,14 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>10-tal bladrosetter</t>
+          <t>på delvis barklös granlåga, nära toppen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,37 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108507992</v>
+        <v>108507994</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625974.6342399252</v>
+        <v>626073</v>
       </c>
       <c r="R6" t="n">
-        <v>6657718.872819177</v>
+        <v>6657628</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1201,19 +1146,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,53 +1175,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108508000</v>
+        <v>111595827</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fallet, Upl</t>
+          <t>Granlunda, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626118.5326694059</v>
+        <v>626208</v>
       </c>
       <c r="R7" t="n">
-        <v>6657670.79329606</v>
+        <v>6657756</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,22 +1243,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1257,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,15 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108507979</v>
+        <v>108507983</v>
       </c>
       <c r="B8" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625949.018836225</v>
+        <v>625936</v>
       </c>
       <c r="R8" t="n">
-        <v>6657779.501584143</v>
+        <v>6657712</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1425,19 +1344,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,15 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108507978</v>
+        <v>108507998</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625948.0524196833</v>
+        <v>626137</v>
       </c>
       <c r="R9" t="n">
-        <v>6657778.468455049</v>
+        <v>6657661</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1537,19 +1441,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,37 +1470,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108508009</v>
+        <v>108508004</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626044.5708979935</v>
+        <v>626167</v>
       </c>
       <c r="R10" t="n">
-        <v>6657826.774165859</v>
+        <v>6657718</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1649,19 +1538,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,100 +1567,94 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108508019</v>
+        <v>111595816</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5733</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fallet, Upl</t>
+          <t>Granlunda, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625984.7864169176</v>
+        <v>626064</v>
       </c>
       <c r="R11" t="n">
-        <v>6657744.222317013</v>
+        <v>6657634</v>
       </c>
       <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Endast artbestämd på utseende och doft, ej mikroskoperad.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
         <v>1</v>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Bälinge</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1800,53 +1673,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108507981</v>
+        <v>111595839</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fallet, Upl</t>
+          <t>Granlunda, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625957.9557484989</v>
+        <v>625947</v>
       </c>
       <c r="R12" t="n">
-        <v>6657781.80742571</v>
+        <v>6657726</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,22 +1741,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,6 +1755,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1912,37 +1774,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108507977</v>
+        <v>108507978</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625926.969083281</v>
+        <v>625949</v>
       </c>
       <c r="R13" t="n">
-        <v>6657721.242812617</v>
+        <v>6657778</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1985,19 +1842,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,37 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108507982</v>
+        <v>108507990</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625947.4520825744</v>
+        <v>625962</v>
       </c>
       <c r="R14" t="n">
-        <v>6657737.444688473</v>
+        <v>6657672</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2097,19 +1939,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,37 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108508010</v>
+        <v>108507979</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626055.3720006796</v>
+        <v>625950</v>
       </c>
       <c r="R15" t="n">
-        <v>6657833.14428748</v>
+        <v>6657780</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2209,24 +2036,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>rotbenet på rötad granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,37 +2065,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108507990</v>
+        <v>108507977</v>
       </c>
       <c r="B16" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625962.214760633</v>
+        <v>625927</v>
       </c>
       <c r="R16" t="n">
-        <v>6657671.943489506</v>
+        <v>6657721</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2326,19 +2133,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,15 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108507993</v>
+        <v>108507980</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626073.4493513135</v>
+        <v>625939</v>
       </c>
       <c r="R17" t="n">
-        <v>6657656.248099978</v>
+        <v>6657785</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2438,19 +2230,14 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,15 +2264,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108507991</v>
+        <v>108507981</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,10 +2299,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625940.5600051499</v>
+        <v>625958</v>
       </c>
       <c r="R18" t="n">
-        <v>6657660.701721931</v>
+        <v>6657781</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2550,19 +2332,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,15 +2361,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108508008</v>
+        <v>108507982</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,10 +2396,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626073.4804819374</v>
+        <v>625948</v>
       </c>
       <c r="R19" t="n">
-        <v>6657816.26315257</v>
+        <v>6657737</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2662,19 +2429,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,15 +2458,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>108508001</v>
+        <v>108507984</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626097.4342639756</v>
+        <v>625934</v>
       </c>
       <c r="R20" t="n">
-        <v>6657672.571011794</v>
+        <v>6657695</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2774,19 +2526,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,12 +2558,7 @@
         <v>108507986</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625926.6417601726</v>
+        <v>625927</v>
       </c>
       <c r="R21" t="n">
-        <v>6657672.226968219</v>
+        <v>6657672</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2886,19 +2623,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,15 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>108507995</v>
+        <v>108507987</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626108.5864305128</v>
+        <v>625959</v>
       </c>
       <c r="R22" t="n">
-        <v>6657639.449242773</v>
+        <v>6657632</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2998,24 +2720,14 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>spridda småplantor</t>
+          <t>10-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,15 +2754,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>108508005</v>
+        <v>108507988</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,10 +2789,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626176.5670760432</v>
+        <v>625930</v>
       </c>
       <c r="R23" t="n">
-        <v>6657731.287184235</v>
+        <v>6657594</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3115,19 +2822,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,37 +2851,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>108508013</v>
+        <v>108507991</v>
       </c>
       <c r="B24" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +2886,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626001.0770924982</v>
+        <v>625941</v>
       </c>
       <c r="R24" t="n">
-        <v>6657868.287983158</v>
+        <v>6657660</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3227,19 +2919,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,15 +2948,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>108508003</v>
+        <v>108507992</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3306,10 +2983,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626153.5362238442</v>
+        <v>625975</v>
       </c>
       <c r="R25" t="n">
-        <v>6657730.998127873</v>
+        <v>6657719</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3339,19 +3016,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,15 +3045,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>108507988</v>
+        <v>108507993</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3418,10 +3080,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>625929.3063272343</v>
+        <v>626073</v>
       </c>
       <c r="R26" t="n">
-        <v>6657594.309347938</v>
+        <v>6657656</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3451,19 +3113,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,15 +3142,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>108508007</v>
+        <v>108507995</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3530,10 +3177,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626136.3331602478</v>
+        <v>626109</v>
       </c>
       <c r="R27" t="n">
-        <v>6657779.91293854</v>
+        <v>6657639</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3563,19 +3210,14 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spridda småplantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,15 +3244,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>108508006</v>
+        <v>108507997</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3642,10 +3279,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626157.3202126378</v>
+        <v>626155</v>
       </c>
       <c r="R28" t="n">
-        <v>6657752.129611494</v>
+        <v>6657644</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3675,19 +3312,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,15 +3341,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>108507987</v>
+        <v>108508000</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3754,10 +3376,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625959.0787799674</v>
+        <v>626119</v>
       </c>
       <c r="R29" t="n">
-        <v>6657631.831909241</v>
+        <v>6657671</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3787,24 +3409,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>10-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,15 +3438,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>108507985</v>
+        <v>108508001</v>
       </c>
       <c r="B30" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,21 +3449,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3473,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625929.9631708378</v>
+        <v>626097</v>
       </c>
       <c r="R30" t="n">
-        <v>6657648.338037907</v>
+        <v>6657672</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3904,24 +3506,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>på delvis barklös granlåga, nära toppen</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,37 +3535,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>108507983</v>
+        <v>108508002</v>
       </c>
       <c r="B31" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,10 +3570,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625935.815811814</v>
+        <v>626084</v>
       </c>
       <c r="R31" t="n">
-        <v>6657711.544466511</v>
+        <v>6657710</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4021,19 +3603,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,15 +3632,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>108508018</v>
+        <v>108508003</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4100,10 +3667,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>626025.7389637282</v>
+        <v>626154</v>
       </c>
       <c r="R32" t="n">
-        <v>6657791.627268632</v>
+        <v>6657731</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4133,19 +3700,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,15 +3729,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>108508012</v>
+        <v>108508005</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4212,10 +3764,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>626016.2860123022</v>
+        <v>626177</v>
       </c>
       <c r="R33" t="n">
-        <v>6657848.307373622</v>
+        <v>6657732</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4245,19 +3797,9 @@
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-04-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,56 +3826,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111595816</v>
+        <v>108508006</v>
       </c>
       <c r="B34" t="n">
-        <v>88948</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5733</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Granlunda, Upl</t>
+          <t>Fallet, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>626063.6952211303</v>
+        <v>626157</v>
       </c>
       <c r="R34" t="n">
-        <v>6657633.911699774</v>
+        <v>6657753</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4357,36 +3891,20 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Endast artbestämd på utseende och doft, ej mikroskoperad.</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4405,57 +3923,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111595763</v>
+        <v>108508007</v>
       </c>
       <c r="B35" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Granlunda, Upl</t>
+          <t>Fallet, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625973.1798164715</v>
+        <v>626136</v>
       </c>
       <c r="R35" t="n">
-        <v>6657702.821588438</v>
+        <v>6657780</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4479,22 +3988,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4503,7 +4002,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4522,56 +4020,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111595839</v>
+        <v>108508008</v>
       </c>
       <c r="B36" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Granlunda, Upl</t>
+          <t>Fallet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625947.8279169253</v>
+        <v>626074</v>
       </c>
       <c r="R36" t="n">
-        <v>6657726.456598986</v>
+        <v>6657816</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4595,22 +4085,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4619,7 +4099,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4635,6 +4114,685 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>108508009</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>626044</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6657827</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>108508011</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>626056</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6657844</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>108508012</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626016</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6657849</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>108508017</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>625954</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6657877</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>108508018</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626026</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6657791</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>108508019</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>625985</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6657744</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>108507996</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fallet, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626156</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6657642</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-04-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
